--- a/reference/governance/sdlc/assets/Evolith_Workbook_F6_Despliegue.xlsx
+++ b/reference/governance/sdlc/assets/Evolith_Workbook_F6_Despliegue.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_Portada" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runbook" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acta_Pase" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,8 +27,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
       <b val="1"/>
-      <color rgb="001E3A5F"/>
+      <color rgb="00CAC5B2"/>
       <sz val="16"/>
     </font>
     <font>
@@ -37,7 +39,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -46,20 +48,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E3A5F"/>
-        <bgColor rgb="001E3A5F"/>
+        <fgColor rgb="00121212"/>
+        <bgColor rgb="00121212"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3F4F6"/>
-        <bgColor rgb="00F3F4F6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="002A2A2A"/>
+        <bgColor rgb="002A2A2A"/>
       </patternFill>
     </fill>
   </fills>
@@ -72,10 +68,18 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color rgb="00CAC5B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CAC5B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CAC5B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CAC5B2"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -83,14 +87,12 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -455,10 +457,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00CAC5B2"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,27 +470,85 @@
           <t>EVOLITH SDLC - Fase 6: Despliegue</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Versión 1.0</t>
         </is>
       </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Nivel de Confidencialidad: Uso Interno</t>
         </is>
       </c>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Instrucciones: Llenar cada pestaña conforme se avanza en la fase correspondiente. Para ser auditado en los Quality Gates.</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Instrucciones: Llenar cada pestaña conforme se avanza en la fase correspondiente.</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -500,153 +561,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Paso</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Rollback</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>1. Backup DB</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Automático</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>DBA</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>Restaurar Snapshot</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>2. Migraciones Flyway</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Automático</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Jenkins</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Rollback SQL</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>3. Despliegue Pods</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Automático</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>ArgoCD</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Revert Git hash</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Proyecto</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Aprobaciones</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Portal Industrial v1.0</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>CAB, QA Lead, Sponsor</t>
         </is>
       </c>
     </row>
